--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484271_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484271_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.0267</v>
+        <v>8.3568</v>
       </c>
       <c r="E2" t="n">
-        <v>6.073</v>
+        <v>7.1852</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9537</v>
+        <v>1.1716</v>
       </c>
       <c r="G2" t="n">
         <v>2.478</v>
@@ -610,13 +610,13 @@
         <v>3.1255</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.5799</v>
+        <v>-0.2497</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1362</v>
+        <v>-0.0239</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4437</v>
+        <v>-0.2258</v>
       </c>
       <c r="V2" t="n">
         <v>5.1517</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7316</v>
+        <v>3.0193</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4757</v>
+        <v>2.9813</v>
       </c>
       <c r="F3" t="n">
-        <v>0.256</v>
+        <v>0.0381</v>
       </c>
       <c r="G3" t="n">
         <v>1.1072</v>
@@ -688,13 +688,13 @@
         <v>2.3441</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0518</v>
+        <v>0.2359</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0384</v>
+        <v>0.4672</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0134</v>
+        <v>-0.2312</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2772</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. ZHURAVLOV</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4798</v>
+        <v>1.8647</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1382</v>
+        <v>1.5993</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.6584</v>
+        <v>0.2655</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2626</v>
+        <v>2.4561</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2502</v>
+        <v>-0.3226</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5128</v>
+        <v>2.7787</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4415</v>
+        <v>3.9041</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.4209</v>
+        <v>0.7201</v>
       </c>
       <c r="L4" t="n">
-        <v>1.8624</v>
+        <v>3.184</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1789</v>
+        <v>-1.448</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1707</v>
+        <v>-1.0427</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.3496</v>
+        <v>-0.4052</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1721</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.3674</v>
+        <v>-5.0789</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5395</v>
+        <v>3.3208</v>
       </c>
       <c r="S4" t="n">
-        <v>2.6507</v>
+        <v>0.6122</v>
       </c>
       <c r="T4" t="n">
-        <v>2.9552</v>
+        <v>0.7238</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3045</v>
+        <v>-0.1116</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.6056</v>
+        <v>0.5545</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1089</v>
+        <v>2.0503</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.7145</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>D. ZHURAVLOV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.133</v>
+        <v>0.6325</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0037</v>
+        <v>2.3182</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1293</v>
+        <v>-1.6857</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4561</v>
+        <v>0.2626</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3226</v>
+        <v>-0.2502</v>
       </c>
       <c r="I5" t="n">
-        <v>2.7787</v>
+        <v>0.5128</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9041</v>
+        <v>1.4415</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7201</v>
+        <v>-0.4209</v>
       </c>
       <c r="L5" t="n">
-        <v>3.184</v>
+        <v>1.8624</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.448</v>
+        <v>-1.1789</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0427</v>
+        <v>0.1707</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4052</v>
+        <v>-1.3496</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="Q5" t="n">
-        <v>-5.0789</v>
+        <v>-1.3674</v>
       </c>
       <c r="R5" t="n">
-        <v>3.3208</v>
+        <v>2.5395</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8804999999999999</v>
+        <v>0.8034</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1282</v>
+        <v>1.1351</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2477</v>
+        <v>-0.3317</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5545</v>
+        <v>-1.6056</v>
       </c>
       <c r="W5" t="n">
-        <v>2.0503</v>
+        <v>1.1089</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.4959</v>
+        <v>-2.7145</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>A. MONTAGUT PUNTI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.2797</v>
+        <v>-1.8127</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3152</v>
+        <v>-3.2661</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.5949</v>
+        <v>1.4534</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2612</v>
+        <v>-3.6509</v>
       </c>
       <c r="H6" t="n">
-        <v>1.8419</v>
+        <v>0.4211</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5807</v>
+        <v>-4.072</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9842</v>
+        <v>-1.9931</v>
       </c>
       <c r="K6" t="n">
-        <v>2.2154</v>
+        <v>1.2689</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7688</v>
+        <v>-3.2619</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.723</v>
+        <v>-1.6579</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3735</v>
+        <v>-0.8478</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3496</v>
+        <v>-0.8101</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.1255</v>
+        <v>-2.3441</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9534</v>
+        <v>2.9301</v>
       </c>
       <c r="S6" t="n">
-        <v>2.6192</v>
+        <v>-0.2985</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7886</v>
+        <v>0.1845</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8306</v>
+        <v>-0.483</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.988</v>
+        <v>1.5507</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3321</v>
+        <v>0.8865</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.6559</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.8906</v>
+        <v>-2.2761</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.3583</v>
+        <v>-1.8528</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5323</v>
+        <v>-0.4233</v>
       </c>
       <c r="G7" t="n">
         <v>-2.061</v>
@@ -1000,13 +1000,13 @@
         <v>1.7581</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1737</v>
+        <v>-0.5592</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5915</v>
+        <v>-0.0859</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5823</v>
+        <v>-0.4733</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2186</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. MONTAGUT PUNTI</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.2712</v>
+        <v>-2.9366</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.4795</v>
+        <v>0.203</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2083</v>
+        <v>-3.1396</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.6509</v>
+        <v>1.2612</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4211</v>
+        <v>1.8419</v>
       </c>
       <c r="I8" t="n">
-        <v>-4.072</v>
+        <v>-0.5807</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.9931</v>
+        <v>2.9842</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2689</v>
+        <v>2.2154</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.2619</v>
+        <v>0.7688</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6579</v>
+        <v>-1.723</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8478</v>
+        <v>-0.3735</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8101</v>
+        <v>-1.3496</v>
       </c>
       <c r="P8" t="n">
-        <v>0.586</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.3441</v>
+        <v>-3.1255</v>
       </c>
       <c r="R8" t="n">
-        <v>2.9301</v>
+        <v>1.9534</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.757</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0289</v>
+        <v>0.6763</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7282</v>
+        <v>0.2859</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5507</v>
+        <v>-3.988</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8865</v>
+        <v>-0.3321</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6642</v>
+        <v>-3.6559</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4392</v>
+        <v>-3.3575</v>
       </c>
       <c r="E9" t="n">
         <v>-2.1817</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2575</v>
+        <v>-1.1758</v>
       </c>
       <c r="G9" t="n">
         <v>-0.5445</v>
@@ -1156,13 +1156,13 @@
         <v>0.586</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3087</v>
+        <v>-0.227</v>
       </c>
       <c r="T9" t="n">
         <v>-0.2283</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0803</v>
+        <v>0.0014</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2186</v>
@@ -1192,16 +1192,16 @@
         <v>3.490399999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>6.9863</v>
+        <v>6.9864</v>
       </c>
       <c r="F10" t="n">
         <v>-3.4958</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3087</v>
+        <v>1.308700000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>-9.999999999998899e-05</v>
+        <v>-9.999999999976694e-05</v>
       </c>
       <c r="I10" t="n">
         <v>1.3087</v>
@@ -1234,13 +1234,13 @@
         <v>18.5575</v>
       </c>
       <c r="S10" t="n">
-        <v>1.279300000000001</v>
+        <v>1.2793</v>
       </c>
       <c r="T10" t="n">
-        <v>2.8487</v>
+        <v>2.8488</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.5695</v>
+        <v>-1.5693</v>
       </c>
       <c r="V10" t="n">
         <v>-1.051099999999999</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>A. RECIO PIÑOL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4.3595</v>
+        <v>4.5522</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0455</v>
+        <v>4.3035</v>
       </c>
       <c r="F11" t="n">
-        <v>2.314</v>
+        <v>0.2486</v>
       </c>
       <c r="G11" t="n">
-        <v>1.62</v>
+        <v>3.268</v>
       </c>
       <c r="H11" t="n">
-        <v>2.362</v>
+        <v>1.2182</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.742</v>
+        <v>2.0497</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4354</v>
+        <v>4.2271</v>
       </c>
       <c r="K11" t="n">
-        <v>1.9071</v>
+        <v>1.6373</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.4718</v>
+        <v>2.5898</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1846</v>
+        <v>-0.9591</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4549</v>
+        <v>-0.419</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2702</v>
+        <v>-0.5401</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9534</v>
+        <v>1.1721</v>
       </c>
       <c r="S11" t="n">
-        <v>2.2204</v>
+        <v>-0.1651</v>
       </c>
       <c r="T11" t="n">
-        <v>2.0444</v>
+        <v>-0.2008</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1759</v>
+        <v>0.0357</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4959</v>
+        <v>0.2772</v>
       </c>
       <c r="W11" t="n">
-        <v>1.4959</v>
+        <v>0.2772</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. RECIO PIÑOL</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.8495</v>
+        <v>3.2459</v>
       </c>
       <c r="E12" t="n">
-        <v>3.8991</v>
+        <v>0.9332</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0496</v>
+        <v>2.3126</v>
       </c>
       <c r="G12" t="n">
-        <v>3.268</v>
+        <v>1.62</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2182</v>
+        <v>2.362</v>
       </c>
       <c r="I12" t="n">
-        <v>2.0497</v>
+        <v>-0.742</v>
       </c>
       <c r="J12" t="n">
-        <v>4.2271</v>
+        <v>1.4354</v>
       </c>
       <c r="K12" t="n">
-        <v>1.6373</v>
+        <v>1.9071</v>
       </c>
       <c r="L12" t="n">
-        <v>2.5898</v>
+        <v>-0.4718</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.9591</v>
+        <v>0.1846</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.419</v>
+        <v>0.4549</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5401</v>
+        <v>-0.2702</v>
       </c>
       <c r="P12" t="n">
-        <v>1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1721</v>
+        <v>1.9534</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8678</v>
+        <v>1.1067</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6052</v>
+        <v>0.9322</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2625</v>
+        <v>0.1746</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2772</v>
+        <v>1.4959</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2772</v>
+        <v>1.4959</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. SUAREZ CANOSA</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.4565</v>
+        <v>1.6338</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4344</v>
+        <v>0.3625</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0221</v>
+        <v>1.2713</v>
       </c>
       <c r="G13" t="n">
-        <v>1.1973</v>
+        <v>1.4131</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6176</v>
+        <v>1.9658</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5797</v>
+        <v>-0.5527</v>
       </c>
       <c r="J13" t="n">
-        <v>1.0024</v>
+        <v>1.3584</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9619</v>
+        <v>1.3712</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0405</v>
+        <v>-0.0128</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1949</v>
+        <v>0.0547</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3443</v>
+        <v>0.5946</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5393</v>
+        <v>-0.5399</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>0.1953</v>
+        <v>1.5627</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0639</v>
+        <v>-0.0881</v>
       </c>
       <c r="T13" t="n">
-        <v>0.432</v>
+        <v>-0.0192</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3681</v>
+        <v>-0.0689</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>M. SUAREZ CANOSA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.0945</v>
+        <v>1.1065</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.042</v>
+        <v>1.0299</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1365</v>
+        <v>0.0766</v>
       </c>
       <c r="G14" t="n">
-        <v>1.4131</v>
+        <v>1.1973</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9658</v>
+        <v>0.6176</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5527</v>
+        <v>0.5797</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3584</v>
+        <v>1.0024</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3712</v>
+        <v>0.9619</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0128</v>
+        <v>0.0405</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0547</v>
+        <v>0.1949</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5946</v>
+        <v>-0.3443</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5399</v>
+        <v>0.5393</v>
       </c>
       <c r="P14" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6274</v>
+        <v>-0.2861</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4237</v>
+        <v>0.0275</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2037</v>
+        <v>-0.3137</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6235000000000001</v>
+        <v>0.8336</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4207</v>
+        <v>-0.3196</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0443</v>
+        <v>1.1532</v>
       </c>
       <c r="G15" t="n">
         <v>2.4905</v>
@@ -1624,13 +1624,13 @@
         <v>1.5627</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4996</v>
+        <v>-0.2896</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0689</v>
+        <v>0.17</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5685</v>
+        <v>-0.4596</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. HERETER MARCHANTE</t>
+          <t>I. ISERN CASES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3741</v>
+        <v>-0.5066000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5823</v>
+        <v>3.3151</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2082</v>
+        <v>-3.8216</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.1853</v>
+        <v>3.3601</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.6841</v>
+        <v>1.7406</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4988</v>
+        <v>1.6194</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.1703</v>
+        <v>4.1289</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.9392</v>
+        <v>2.374</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7688</v>
+        <v>1.7548</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.015</v>
+        <v>-0.7688</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2551</v>
+        <v>-0.6334</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.27</v>
+        <v>-0.1354</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7814</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R16" t="n">
         <v>1.7581</v>
       </c>
       <c r="S16" t="n">
-        <v>0.307</v>
+        <v>-0.9568</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0689</v>
+        <v>-0.079</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2381</v>
+        <v>-0.8778</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2772</v>
+        <v>-2.7145</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4959</v>
+        <v>1.2186</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.7731</v>
+        <v>-3.9331</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. ISERN CASES</t>
+          <t>G. HERETER MARCHANTE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2144</v>
+        <v>-0.6867</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6073</v>
+        <v>-0.7845</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.8216</v>
+        <v>0.0979</v>
       </c>
       <c r="G17" t="n">
-        <v>3.3601</v>
+        <v>-1.1853</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7406</v>
+        <v>-1.6841</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6194</v>
+        <v>0.4988</v>
       </c>
       <c r="J17" t="n">
-        <v>4.1289</v>
+        <v>-1.1703</v>
       </c>
       <c r="K17" t="n">
-        <v>2.374</v>
+        <v>-1.9392</v>
       </c>
       <c r="L17" t="n">
-        <v>1.7548</v>
+        <v>0.7688</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7688</v>
+        <v>-0.015</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6334</v>
+        <v>0.2551</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1354</v>
+        <v>-0.27</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
         <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.6646</v>
+        <v>-0.0055</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.1334</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8778</v>
+        <v>0.1278</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.7145</v>
+        <v>-0.2772</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2186</v>
+        <v>1.4959</v>
       </c>
       <c r="X17" t="n">
-        <v>-3.9331</v>
+        <v>-1.7731</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. PUERTAS GARCIA</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6226</v>
+        <v>-1.6903</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0884</v>
+        <v>-0.3548</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.711</v>
+        <v>-1.3355</v>
       </c>
       <c r="G18" t="n">
-        <v>-5.0116</v>
+        <v>-1.563</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.042</v>
+        <v>-0.6188</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.9696</v>
+        <v>-0.9441000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.5357</v>
+        <v>0.7595</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.59</v>
+        <v>0.0844</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0543</v>
+        <v>0.6751</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.4759</v>
+        <v>-2.3225</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.452</v>
+        <v>-0.7032</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.0239</v>
+        <v>-1.6192</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5627</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8849</v>
+        <v>0.1582</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1282</v>
+        <v>0.0428</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2433</v>
+        <v>0.1154</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9414</v>
+        <v>0.8865</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4959</v>
+        <v>1.7731</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5545</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>A. JAIME BATLLE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.755</v>
+        <v>-1.9586</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.9579</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.198</v>
+        <v>-1.0007</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.563</v>
+        <v>-3.8236</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6188</v>
+        <v>-1.1136</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9441000000000001</v>
+        <v>-2.71</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7595</v>
+        <v>-1.3712</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0844</v>
+        <v>-0.55</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6751</v>
+        <v>-0.8212</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.3225</v>
+        <v>-2.4524</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7032</v>
+        <v>-0.5636</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.6192</v>
+        <v>-1.8889</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
         <v>1.7581</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0935</v>
+        <v>-0.1898</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1594</v>
+        <v>-0.1058</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2529</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>0.8865</v>
+        <v>1.2735</v>
       </c>
       <c r="W19" t="n">
-        <v>1.7731</v>
+        <v>1.4959</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.8865</v>
+        <v>-0.2224</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. JAIME BATLLE</t>
+          <t>A. PUERTAS GARCIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9193</v>
+        <v>-2.3382</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5645</v>
+        <v>0.4817</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3548</v>
+        <v>-2.8199</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.8236</v>
+        <v>-5.0116</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1136</v>
+        <v>-3.042</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.71</v>
+        <v>-1.9696</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3712</v>
+        <v>-1.5357</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.55</v>
+        <v>-1.59</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.8212</v>
+        <v>0.0543</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.4524</v>
+        <v>-3.4759</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5636</v>
+        <v>-1.452</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.8889</v>
+        <v>-2.0239</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7814</v>
+        <v>1.5627</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1506</v>
+        <v>0.1693</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7125</v>
+        <v>0.5215</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4381</v>
+        <v>-0.3523</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2735</v>
+        <v>0.9414</v>
       </c>
       <c r="W20" t="n">
         <v>1.4959</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2224</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.029</v>
+        <v>-7.0484</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.4121</v>
+        <v>-4.5132</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.6168</v>
+        <v>-2.5351</v>
       </c>
       <c r="G21" t="n">
         <v>-3.1147</v>
@@ -2092,13 +2092,13 @@
         <v>1.5627</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.039</v>
+        <v>-0.0584</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5147</v>
+        <v>0.4135</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5537</v>
+        <v>-0.472</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5545</v>
@@ -2125,16 +2125,16 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.5309</v>
+        <v>-2.856800000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>3.4961</v>
+        <v>3.4959</v>
       </c>
       <c r="F22" t="n">
-        <v>-7.0267</v>
+        <v>-6.352599999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.349199999999999</v>
+        <v>-1.3492</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -2158,7 +2158,7 @@
         <v>-3.938</v>
       </c>
       <c r="O22" t="n">
-        <v>-7.424000000000001</v>
+        <v>-7.423999999999999</v>
       </c>
       <c r="P22" t="n">
         <v>-1.9534</v>
@@ -2170,13 +2170,13 @@
         <v>16.604</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2793</v>
+        <v>-0.6052</v>
       </c>
       <c r="T22" t="n">
-        <v>1.5695</v>
+        <v>1.5693</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.8488</v>
+        <v>-2.1748</v>
       </c>
       <c r="V22" t="n">
         <v>1.0511</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484271_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484271_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484271_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,11 +715,16 @@
       <c r="X3" t="n">
         <v>-0.8317</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484271_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>P. MONES RIERA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,28 +736,28 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8647</v>
+        <v>1.5577</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5993</v>
+        <v>1.2923</v>
       </c>
       <c r="F4" t="n">
         <v>0.2655</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4561</v>
+        <v>2.1491</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3226</v>
+        <v>-0.6296</v>
       </c>
       <c r="I4" t="n">
         <v>2.7787</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9041</v>
+        <v>3.5971</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7201</v>
+        <v>0.4131</v>
       </c>
       <c r="L4" t="n">
         <v>3.184</v>
@@ -782,6 +797,11 @@
       </c>
       <c r="X4" t="n">
         <v>-1.4959</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484271_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -861,11 +881,16 @@
       <c r="X5" t="n">
         <v>-2.7145</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484271_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MONTAGUT PUNTI</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.8127</v>
+        <v>0.307</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.2661</v>
+        <v>0.307</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4534</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.6509</v>
+        <v>0.307</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4211</v>
+        <v>0.307</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.072</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.9931</v>
+        <v>0.307</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2689</v>
+        <v>0.307</v>
       </c>
       <c r="L6" t="n">
-        <v>-3.2619</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6579</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8478</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8101</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.3441</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.9301</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2985</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1845</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.483</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5507</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484271_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>A. MONTAGUT PUNTI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2761</v>
+        <v>-1.8127</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8528</v>
+        <v>-3.2661</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4233</v>
+        <v>1.4534</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.061</v>
+        <v>-3.6509</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.1804</v>
+        <v>0.4211</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1194</v>
+        <v>-4.072</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.5715</v>
+        <v>-1.9931</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.9612</v>
+        <v>1.2689</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3897</v>
+        <v>-3.2619</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4895</v>
+        <v>-1.6579</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2192</v>
+        <v>-0.8478</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2702</v>
+        <v>-0.8101</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1953</v>
+        <v>-2.3441</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7581</v>
+        <v>2.9301</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5592</v>
+        <v>-0.2985</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0859</v>
+        <v>0.1845</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4733</v>
+        <v>-0.483</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2186</v>
+        <v>1.5507</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2186</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484271_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.9366</v>
+        <v>-2.2761</v>
       </c>
       <c r="E8" t="n">
-        <v>0.203</v>
+        <v>-1.8528</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.1396</v>
+        <v>-0.4233</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2612</v>
+        <v>-2.061</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8419</v>
+        <v>-3.1804</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5807</v>
+        <v>1.1194</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9842</v>
+        <v>-1.5715</v>
       </c>
       <c r="K8" t="n">
-        <v>2.2154</v>
+        <v>-2.9612</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7688</v>
+        <v>1.3897</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.723</v>
+        <v>-0.4895</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3735</v>
+        <v>-0.2192</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.3496</v>
+        <v>-0.2702</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.1255</v>
+        <v>-0.1953</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9534</v>
+        <v>1.7581</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9622000000000001</v>
+        <v>-0.5592</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6763</v>
+        <v>-0.0859</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2859</v>
+        <v>-0.4733</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.988</v>
+        <v>-1.2186</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.6559</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484271_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3575</v>
+        <v>-2.9366</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1817</v>
+        <v>0.203</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1758</v>
+        <v>-3.1396</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5445</v>
+        <v>1.2612</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0049</v>
+        <v>1.8419</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5397</v>
+        <v>-0.5807</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2.9842</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2.2154</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.7688</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5445</v>
+        <v>-1.723</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0049</v>
+        <v>-0.3735</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5397</v>
+        <v>-1.3496</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.3674</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9534</v>
+        <v>-3.1255</v>
       </c>
       <c r="R9" t="n">
-        <v>0.586</v>
+        <v>1.9534</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.227</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2283</v>
+        <v>0.6763</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0014</v>
+        <v>0.2859</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2186</v>
+        <v>-3.988</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2186</v>
+        <v>-3.6559</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484271_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,184 +1234,190 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>3.490399999999999</v>
+        <v>-3.3575</v>
       </c>
       <c r="E10" t="n">
-        <v>6.9864</v>
+        <v>-2.1817</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.4958</v>
+        <v>-1.1758</v>
       </c>
       <c r="G10" t="n">
-        <v>1.308700000000001</v>
+        <v>-0.5445</v>
       </c>
       <c r="H10" t="n">
-        <v>-9.999999999976694e-05</v>
+        <v>-0.0049</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3087</v>
+        <v>-0.5397</v>
       </c>
       <c r="J10" t="n">
-        <v>11.3216</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9381</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>7.3836</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-10.013</v>
+        <v>-0.5445</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.9382</v>
+        <v>-0.0049</v>
       </c>
       <c r="O10" t="n">
-        <v>-6.0748</v>
+        <v>-0.5397</v>
       </c>
       <c r="P10" t="n">
-        <v>1.9533</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q10" t="n">
-        <v>-16.6041</v>
+        <v>-1.9534</v>
       </c>
       <c r="R10" t="n">
-        <v>18.5575</v>
+        <v>0.586</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2793</v>
+        <v>-0.227</v>
       </c>
       <c r="T10" t="n">
-        <v>2.8488</v>
+        <v>-0.2283</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.5693</v>
+        <v>0.0014</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.051099999999999</v>
+        <v>-1.2186</v>
       </c>
       <c r="W10" t="n">
-        <v>9.4198</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-10.471</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484271_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. RECIO PIÑOL</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>CB NAVÀS VISCOLA</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4.5522</v>
+        <v>3.490399999999998</v>
       </c>
       <c r="E11" t="n">
-        <v>4.3035</v>
+        <v>6.986399999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2486</v>
+        <v>-3.495799999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>3.268</v>
+        <v>1.3087</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2182</v>
+        <v>-9.999999999997337e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>2.0497</v>
+        <v>1.3087</v>
       </c>
       <c r="J11" t="n">
-        <v>4.2271</v>
+        <v>11.3216</v>
       </c>
       <c r="K11" t="n">
-        <v>1.6373</v>
+        <v>3.9381</v>
       </c>
       <c r="L11" t="n">
-        <v>2.5898</v>
+        <v>7.3836</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.9591</v>
+        <v>-10.013</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.419</v>
+        <v>-3.9382</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5401</v>
+        <v>-6.0748</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1721</v>
+        <v>1.9533</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-16.6041</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1721</v>
+        <v>18.5575</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1651</v>
+        <v>1.2793</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2008</v>
+        <v>2.8488</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0357</v>
+        <v>-1.5693</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2772</v>
+        <v>-1.051099999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2772</v>
+        <v>9.4198</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
-      </c>
+        <v>-10.471</v>
+      </c>
+      <c r="Y11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>A. ABELLO GIRVES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.2459</v>
+        <v>2.6319</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9332</v>
+        <v>0.3193</v>
       </c>
       <c r="F12" t="n">
         <v>2.3126</v>
       </c>
       <c r="G12" t="n">
-        <v>1.62</v>
+        <v>1.006</v>
       </c>
       <c r="H12" t="n">
-        <v>2.362</v>
+        <v>1.748</v>
       </c>
       <c r="I12" t="n">
         <v>-0.742</v>
       </c>
       <c r="J12" t="n">
-        <v>1.4354</v>
+        <v>0.8214</v>
       </c>
       <c r="K12" t="n">
-        <v>1.9071</v>
+        <v>1.2931</v>
       </c>
       <c r="L12" t="n">
         <v>-0.4718</v>
@@ -1406,787 +1457,1170 @@
       </c>
       <c r="X12" t="n">
         <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484271_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>A. RECIO PIÑOL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.6338</v>
+        <v>2.4279</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3625</v>
+        <v>2.4279</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2713</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>1.4131</v>
+        <v>2.4279</v>
       </c>
       <c r="H13" t="n">
-        <v>1.9658</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5527</v>
+        <v>2.4279</v>
       </c>
       <c r="J13" t="n">
-        <v>1.3584</v>
+        <v>2.4279</v>
       </c>
       <c r="K13" t="n">
-        <v>1.3712</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.0128</v>
+        <v>2.4279</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0547</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5946</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5399</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0881</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0192</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0689</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484271_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. SUAREZ CANOSA</t>
+          <t>A. RECIO PINOL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1065</v>
+        <v>2.1242</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0299</v>
+        <v>1.8756</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0766</v>
+        <v>0.2486</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1973</v>
+        <v>0.84</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6176</v>
+        <v>1.2182</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5797</v>
+        <v>-0.3782</v>
       </c>
       <c r="J14" t="n">
-        <v>1.0024</v>
+        <v>1.7991</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9619</v>
+        <v>1.6373</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0405</v>
+        <v>0.1619</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1949</v>
+        <v>-0.9591</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3443</v>
+        <v>-0.419</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5393</v>
+        <v>-0.5401</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2861</v>
+        <v>-0.1651</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0275</v>
+        <v>-0.2008</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3137</v>
+        <v>0.0357</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484271_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>H. DEL RIO GASPAR</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8336</v>
+        <v>1.6338</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.3196</v>
+        <v>0.3625</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1532</v>
+        <v>1.2713</v>
       </c>
       <c r="G15" t="n">
-        <v>2.4905</v>
+        <v>1.4131</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0207</v>
+        <v>1.9658</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4698</v>
+        <v>-0.5527</v>
       </c>
       <c r="J15" t="n">
-        <v>2.4405</v>
+        <v>1.3584</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1051</v>
+        <v>1.3712</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3354</v>
+        <v>-0.0128</v>
       </c>
       <c r="M15" t="n">
-        <v>0.05</v>
+        <v>0.0547</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0844</v>
+        <v>0.5946</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1344</v>
+        <v>-0.5399</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
         <v>1.5627</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2896</v>
+        <v>-0.0881</v>
       </c>
       <c r="T15" t="n">
-        <v>0.17</v>
+        <v>-0.0192</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4596</v>
+        <v>-0.0689</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484271_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. ISERN CASES</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5066000000000001</v>
+        <v>1.221</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3151</v>
+        <v>1.221</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.8216</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>3.3601</v>
+        <v>1.221</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7406</v>
+        <v>0.614</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6194</v>
+        <v>0.607</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1289</v>
+        <v>1.221</v>
       </c>
       <c r="K16" t="n">
-        <v>2.374</v>
+        <v>0.614</v>
       </c>
       <c r="L16" t="n">
-        <v>1.7548</v>
+        <v>0.607</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7688</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6334</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1354</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9568</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.079</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8778</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.7145</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.9331</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484271_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. HERETER MARCHANTE</t>
+          <t>M. SUAREZ CANOSA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6867</v>
+        <v>1.1065</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7845</v>
+        <v>1.0299</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0979</v>
+        <v>0.0766</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1853</v>
+        <v>1.1973</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.6841</v>
+        <v>0.6176</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4988</v>
+        <v>0.5797</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.1703</v>
+        <v>1.0024</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.9392</v>
+        <v>0.9619</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7688</v>
+        <v>0.0405</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.015</v>
+        <v>0.1949</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2551</v>
+        <v>-0.3443</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.27</v>
+        <v>0.5393</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7581</v>
+        <v>0.1953</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0055</v>
+        <v>-0.2861</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1334</v>
+        <v>0.0275</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1278</v>
+        <v>-0.3137</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.7731</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484271_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>H. DEL RIO GASPAR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6903</v>
+        <v>0.8336</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3548</v>
+        <v>-0.3196</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3355</v>
+        <v>1.1532</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.563</v>
+        <v>2.4905</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6188</v>
+        <v>1.0207</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9441000000000001</v>
+        <v>1.4698</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7595</v>
+        <v>2.4405</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0844</v>
+        <v>1.1051</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6751</v>
+        <v>1.3354</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.3225</v>
+        <v>0.05</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7032</v>
+        <v>-0.0844</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.6192</v>
+        <v>0.1344</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1721</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q18" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1582</v>
+        <v>-0.2896</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0428</v>
+        <v>0.17</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1154</v>
+        <v>-0.4596</v>
       </c>
       <c r="V18" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.7731</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484271_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. JAIME BATLLE</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9586</v>
+        <v>0.614</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9579</v>
+        <v>0.614</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0007</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.8236</v>
+        <v>0.614</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1136</v>
+        <v>0.614</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.71</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.3712</v>
+        <v>0.614</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.55</v>
+        <v>0.614</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.8212</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.4524</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5636</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.8889</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1898</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1058</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.08400000000000001</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2735</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2224</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484271_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. PUERTAS GARCIA</t>
+          <t>I. ISERN CASES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3382</v>
+        <v>-0.5066000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4817</v>
+        <v>3.3151</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.8199</v>
+        <v>-3.8216</v>
       </c>
       <c r="G20" t="n">
-        <v>-5.0116</v>
+        <v>3.3601</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.042</v>
+        <v>1.7406</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.9696</v>
+        <v>1.6194</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.5357</v>
+        <v>4.1289</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.59</v>
+        <v>2.374</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0543</v>
+        <v>1.7548</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.4759</v>
+        <v>-0.7688</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.452</v>
+        <v>-0.6334</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.0239</v>
+        <v>-0.1354</v>
       </c>
       <c r="P20" t="n">
-        <v>1.5627</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1693</v>
+        <v>-0.9568</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5215</v>
+        <v>-0.079</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3523</v>
+        <v>-0.8778</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9414</v>
+        <v>-2.7145</v>
       </c>
       <c r="W20" t="n">
-        <v>1.4959</v>
+        <v>1.2186</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5545</v>
+        <v>-3.9331</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484271_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. VILAR FERNANDEZ</t>
+          <t>G. HERETER MARCHANTE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.0484</v>
+        <v>-0.6867</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.5132</v>
+        <v>-0.7845</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.5351</v>
+        <v>0.0979</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.1147</v>
+        <v>-1.1853</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.4664</v>
+        <v>-1.6841</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6482</v>
+        <v>0.4988</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2619</v>
+        <v>-1.1703</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.4237</v>
+        <v>-1.9392</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1619</v>
+        <v>0.7688</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8528</v>
+        <v>-0.015</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0427</v>
+        <v>0.2551</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8101</v>
+        <v>-0.27</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.3208</v>
+        <v>0.7814</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.8836</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0584</v>
+        <v>-0.0055</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4135</v>
+        <v>-0.1334</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.472</v>
+        <v>0.1278</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5545</v>
+        <v>-0.2772</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2186</v>
+        <v>1.4959</v>
       </c>
       <c r="X21" t="n">
         <v>-1.7731</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484271_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. JAIME BATLLE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.856800000000001</v>
+        <v>-1.9586</v>
       </c>
       <c r="E22" t="n">
-        <v>3.4959</v>
+        <v>-0.9579</v>
       </c>
       <c r="F22" t="n">
+        <v>-1.0007</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-3.8236</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-1.1136</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-2.71</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-1.3712</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-0.8212</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-2.4524</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.5636</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-1.8889</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-0.1898</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-0.1058</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-0.08400000000000001</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.2735</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.4959</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-0.2224</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484271_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A. PUERTAS GARCIA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-2.3382</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.4817</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-2.8199</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-5.0116</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-3.042</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-1.9696</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-1.5357</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.0543</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-3.4759</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-1.452</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-2.0239</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.1693</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.5215</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.3523</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.9414</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.4959</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-0.5545</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484271_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>P. CARRION SORIANO</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-2.9112</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-1.5757</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-1.3355</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-2.7839</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-1.2328</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-1.5511</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-0.4615</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.5296</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.06809999999999999</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-2.3225</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.7032</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-1.6192</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.1582</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.0428</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.1154</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.8865</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.7731</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-0.8865</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484271_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>F. VILAR FERNANDEZ</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-7.0484</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-4.5132</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-2.5351</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-3.1147</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-2.4664</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.6482</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-1.2619</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-1.4237</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1.8528</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-1.0427</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.8101</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-3.3208</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-4.8836</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.0584</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.4135</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.472</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-0.5545</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-1.7731</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484271_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-2.856800000000002</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3.496100000000001</v>
+      </c>
+      <c r="F26" t="n">
         <v>-6.352599999999999</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G26" t="n">
         <v>-1.3492</v>
       </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>-1.3492</v>
-      </c>
-      <c r="J22" t="n">
-        <v>10.0131</v>
-      </c>
-      <c r="K22" t="n">
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-1.349199999999999</v>
+      </c>
+      <c r="J26" t="n">
+        <v>10.013</v>
+      </c>
+      <c r="K26" t="n">
         <v>3.938099999999999</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L26" t="n">
         <v>6.0748</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M26" t="n">
         <v>-11.3623</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N26" t="n">
         <v>-3.938</v>
       </c>
-      <c r="O22" t="n">
-        <v>-7.423999999999999</v>
-      </c>
-      <c r="P22" t="n">
+      <c r="O26" t="n">
+        <v>-7.424</v>
+      </c>
+      <c r="P26" t="n">
         <v>-1.9534</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q26" t="n">
         <v>-18.5574</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R26" t="n">
         <v>16.604</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S26" t="n">
         <v>-0.6052</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T26" t="n">
         <v>1.5693</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U26" t="n">
         <v>-2.1748</v>
       </c>
-      <c r="V22" t="n">
+      <c r="V26" t="n">
         <v>1.0511</v>
       </c>
-      <c r="W22" t="n">
+      <c r="W26" t="n">
         <v>10.4711</v>
       </c>
-      <c r="X22" t="n">
+      <c r="X26" t="n">
         <v>-9.4199</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
